--- a/data/haver_pivoted.xlsx
+++ b/data/haver_pivoted.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr date1904="false"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
@@ -644,196 +644,196 @@
     <t xml:space="preserve">gdp</t>
   </si>
   <si>
-    <t xml:space="preserve">gdph</t>
+    <t xml:space="preserve">real_gdp</t>
   </si>
   <si>
-    <t xml:space="preserve">jgdp</t>
+    <t xml:space="preserve">gdp_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">c</t>
+    <t xml:space="preserve">consumption</t>
   </si>
   <si>
-    <t xml:space="preserve">ch</t>
+    <t xml:space="preserve">real_consumption</t>
   </si>
   <si>
-    <t xml:space="preserve">jc</t>
+    <t xml:space="preserve">consumption_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">jgf</t>
+    <t xml:space="preserve">federal_purchases_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">jgs</t>
+    <t xml:space="preserve">state_purchases_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">jgse</t>
+    <t xml:space="preserve">consumption_grants_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">jgsi</t>
+    <t xml:space="preserve">investment_grants_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">yptmr</t>
+    <t xml:space="preserve">medicare</t>
   </si>
   <si>
-    <t xml:space="preserve">yptmd</t>
+    <t xml:space="preserve">medicaid</t>
   </si>
   <si>
-    <t xml:space="preserve">yptu</t>
+    <t xml:space="preserve">ui</t>
   </si>
   <si>
-    <t xml:space="preserve">gtfp</t>
+    <t xml:space="preserve">social_benefits</t>
   </si>
   <si>
-    <t xml:space="preserve">ypog</t>
+    <t xml:space="preserve">paymentPersonal</t>
   </si>
   <si>
-    <t xml:space="preserve">yptx</t>
+    <t xml:space="preserve">personal_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">ytpi</t>
+    <t xml:space="preserve">production_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">yctlg</t>
+    <t xml:space="preserve">corporate_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">g</t>
+    <t xml:space="preserve">purchases</t>
   </si>
   <si>
-    <t xml:space="preserve">grcsi</t>
+    <t xml:space="preserve">paymentSocialInsurance</t>
   </si>
   <si>
     <t xml:space="preserve">dc</t>
   </si>
   <si>
-    <t xml:space="preserve">gf</t>
+    <t xml:space="preserve">federal_purchases</t>
   </si>
   <si>
-    <t xml:space="preserve">gs</t>
+    <t xml:space="preserve">state_purchases</t>
   </si>
   <si>
-    <t xml:space="preserve">gfh</t>
+    <t xml:space="preserve">real_federal_purchases</t>
   </si>
   <si>
-    <t xml:space="preserve">gsh</t>
+    <t xml:space="preserve">real_state_purchases</t>
   </si>
   <si>
-    <t xml:space="preserve">gfrpt</t>
+    <t xml:space="preserve">federal_personal_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gfrpri</t>
+    <t xml:space="preserve">federal_production_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gfrcp</t>
+    <t xml:space="preserve">federal_corporate_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gfrs</t>
+    <t xml:space="preserve">federal_payroll_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfp</t>
+    <t xml:space="preserve">federal_social_benefits</t>
   </si>
   <si>
-    <t xml:space="preserve">gfeg</t>
+    <t xml:space="preserve">gross_consumption_grants</t>
   </si>
   <si>
-    <t xml:space="preserve">gsrpt</t>
+    <t xml:space="preserve">state_personal_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gsrpri</t>
+    <t xml:space="preserve">state_production_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gsrcp</t>
+    <t xml:space="preserve">state_corporate_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gsrs</t>
+    <t xml:space="preserve">state_payroll_taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">gstfp</t>
+    <t xml:space="preserve">state_social_benefits</t>
   </si>
   <si>
-    <t xml:space="preserve">gset</t>
+    <t xml:space="preserve">state_expenditures</t>
   </si>
   <si>
-    <t xml:space="preserve">gfeghhx</t>
+    <t xml:space="preserve">health_grants</t>
   </si>
   <si>
-    <t xml:space="preserve">gfeghdx</t>
+    <t xml:space="preserve">medicaid_grants</t>
   </si>
   <si>
-    <t xml:space="preserve">gfeigx</t>
+    <t xml:space="preserve">investment_grants</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsub</t>
+    <t xml:space="preserve">federal_subsidies</t>
   </si>
   <si>
-    <t xml:space="preserve">gssub</t>
+    <t xml:space="preserve">state_subsidies</t>
   </si>
   <si>
-    <t xml:space="preserve">gsub</t>
+    <t xml:space="preserve">subsidies</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfpe</t>
+    <t xml:space="preserve">rebate_checks</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfpr</t>
+    <t xml:space="preserve">medicare_reimbursement_increase</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfpp</t>
+    <t xml:space="preserve">nonprofit_ppp</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfpv</t>
+    <t xml:space="preserve">nonprofit_provider_relief_fund</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubp</t>
+    <t xml:space="preserve">ppp</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubg</t>
+    <t xml:space="preserve">aviation</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsube</t>
+    <t xml:space="preserve">employee_retention</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubs</t>
+    <t xml:space="preserve">transit</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubf</t>
+    <t xml:space="preserve">coronavirus_food_assistance</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubv</t>
+    <t xml:space="preserve">provider_relief_fund</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubk</t>
+    <t xml:space="preserve">paid_sick_leave</t>
   </si>
   <si>
-    <t xml:space="preserve">gfegc</t>
+    <t xml:space="preserve">coronavirus_relief_fund</t>
   </si>
   <si>
-    <t xml:space="preserve">gfege</t>
+    <t xml:space="preserve">education_stabilization_fund</t>
   </si>
   <si>
-    <t xml:space="preserve">gfegv</t>
+    <t xml:space="preserve">provider_relief_fund_grants</t>
   </si>
   <si>
-    <t xml:space="preserve">yptue</t>
+    <t xml:space="preserve">peuc</t>
   </si>
   <si>
-    <t xml:space="preserve">yptup</t>
+    <t xml:space="preserve">pua</t>
   </si>
   <si>
-    <t xml:space="preserve">yptuc</t>
+    <t xml:space="preserve">puc</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfpu</t>
+    <t xml:space="preserve">ui_expansion</t>
   </si>
   <si>
-    <t xml:space="preserve">yptub</t>
+    <t xml:space="preserve">ui_extended_benefits</t>
   </si>
   <si>
-    <t xml:space="preserve">yptol</t>
+    <t xml:space="preserve">wages_lost_assistance</t>
   </si>
   <si>
-    <t xml:space="preserve">gfctp</t>
+    <t xml:space="preserve">capital_transfer_payments</t>
   </si>
   <si>
-    <t xml:space="preserve">gftffx</t>
+    <t xml:space="preserve">snap</t>
   </si>
   <si>
     <t xml:space="preserve">cpiu</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">pcw</t>
   </si>
   <si>
-    <t xml:space="preserve">gdppothq</t>
+    <t xml:space="preserve">real_potential_gdp_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">gdppotq</t>
+    <t xml:space="preserve">potential_gdp_growth</t>
   </si>
   <si>
     <t xml:space="preserve">recessq</t>
@@ -860,46 +860,46 @@
     <t xml:space="preserve">cpgs</t>
   </si>
   <si>
-    <t xml:space="preserve">jgdp_growth</t>
+    <t xml:space="preserve">gdp_deflator_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">jc_growth</t>
+    <t xml:space="preserve">consumption_deflator_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">jgf_growth</t>
+    <t xml:space="preserve">federal_purchases_deflator_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">jgs_growth</t>
+    <t xml:space="preserve">state_purchases_deflator_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">jgse_growth</t>
+    <t xml:space="preserve">consumption_grants_deflator_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">jgsi_growth</t>
+    <t xml:space="preserve">investment_grants_deflator_growth</t>
   </si>
   <si>
-    <t xml:space="preserve">ylwsd</t>
+    <t xml:space="preserve">wages_and_salaries</t>
   </si>
   <si>
-    <t xml:space="preserve">yop</t>
+    <t xml:space="preserve">proprietors_income</t>
   </si>
   <si>
-    <t xml:space="preserve">yri</t>
+    <t xml:space="preserve">rental_income</t>
   </si>
   <si>
-    <t xml:space="preserve">ypiar</t>
+    <t xml:space="preserve">asset_income</t>
   </si>
   <si>
-    <t xml:space="preserve">ycpd</t>
+    <t xml:space="preserve">corporate_profits</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubr</t>
+    <t xml:space="preserve">restaurant_revitalization_fund</t>
   </si>
   <si>
-    <t xml:space="preserve">gfsubd</t>
+    <t xml:space="preserve">disaster_loans</t>
   </si>
   <si>
-    <t xml:space="preserve">gftfbdx</t>
+    <t xml:space="preserve">social_security</t>
   </si>
   <si>
     <t xml:space="preserve">yptocm</t>
@@ -908,7 +908,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
@@ -1227,7 +1227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
@@ -25230,352 +25230,352 @@
       <c r="CN39"/>
       <c r="CO39"/>
       <c r="CP39" t="n">
-        <v>78.072</v>
+        <v>78072</v>
       </c>
       <c r="CQ39" t="n">
-        <v>80.831</v>
+        <v>80831</v>
       </c>
       <c r="CR39" t="n">
-        <v>85.251</v>
+        <v>85251</v>
       </c>
       <c r="CS39" t="n">
-        <v>88.178</v>
+        <v>88178</v>
       </c>
       <c r="CT39" t="n">
-        <v>84.002</v>
+        <v>84002</v>
       </c>
       <c r="CU39" t="n">
-        <v>86.255</v>
+        <v>86255</v>
       </c>
       <c r="CV39" t="n">
-        <v>87.978</v>
+        <v>87978</v>
       </c>
       <c r="CW39" t="n">
-        <v>89.829</v>
+        <v>89829</v>
       </c>
       <c r="CX39" t="n">
-        <v>95.218</v>
+        <v>95218</v>
       </c>
       <c r="CY39" t="n">
-        <v>94.484</v>
+        <v>94484</v>
       </c>
       <c r="CZ39" t="n">
-        <v>93.858</v>
+        <v>93858</v>
       </c>
       <c r="DA39" t="n">
-        <v>92.181</v>
+        <v>92181</v>
       </c>
       <c r="DB39" t="n">
-        <v>94.539</v>
+        <v>94539</v>
       </c>
       <c r="DC39" t="n">
-        <v>102.461</v>
+        <v>102461</v>
       </c>
       <c r="DD39" t="n">
-        <v>99.672</v>
+        <v>99672</v>
       </c>
       <c r="DE39" t="n">
-        <v>97.609</v>
+        <v>97609</v>
       </c>
       <c r="DF39" t="n">
-        <v>98.691</v>
+        <v>98691</v>
       </c>
       <c r="DG39" t="n">
-        <v>98.642</v>
+        <v>98642</v>
       </c>
       <c r="DH39" t="n">
-        <v>101.001</v>
+        <v>101001</v>
       </c>
       <c r="DI39" t="n">
-        <v>105.738</v>
+        <v>105738</v>
       </c>
       <c r="DJ39" t="n">
-        <v>103.992</v>
+        <v>103992</v>
       </c>
       <c r="DK39" t="n">
-        <v>106.287</v>
+        <v>106287</v>
       </c>
       <c r="DL39" t="n">
-        <v>106.646</v>
+        <v>106646</v>
       </c>
       <c r="DM39" t="n">
-        <v>110.762</v>
+        <v>110762</v>
       </c>
       <c r="DN39" t="n">
-        <v>114.027</v>
+        <v>114027</v>
       </c>
       <c r="DO39" t="n">
-        <v>113.559</v>
+        <v>113559</v>
       </c>
       <c r="DP39" t="n">
-        <v>120.524</v>
+        <v>120524</v>
       </c>
       <c r="DQ39" t="n">
-        <v>121.904</v>
+        <v>121904</v>
       </c>
       <c r="DR39" t="n">
-        <v>121.898</v>
+        <v>121898</v>
       </c>
       <c r="DS39" t="n">
-        <v>123.319</v>
+        <v>123319</v>
       </c>
       <c r="DT39" t="n">
-        <v>133.626</v>
+        <v>133626</v>
       </c>
       <c r="DU39" t="n">
-        <v>129.622</v>
+        <v>129622</v>
       </c>
       <c r="DV39" t="n">
-        <v>138.716</v>
+        <v>138716</v>
       </c>
       <c r="DW39" t="n">
-        <v>145.774</v>
+        <v>145774</v>
       </c>
       <c r="DX39" t="n">
-        <v>143.219</v>
+        <v>143219</v>
       </c>
       <c r="DY39" t="n">
-        <v>153.809</v>
+        <v>153809</v>
       </c>
       <c r="DZ39" t="n">
-        <v>156.084</v>
+        <v>156084</v>
       </c>
       <c r="EA39" t="n">
-        <v>157.455</v>
+        <v>157455</v>
       </c>
       <c r="EB39" t="n">
-        <v>164.01</v>
+        <v>164010</v>
       </c>
       <c r="EC39" t="n">
-        <v>166.934</v>
+        <v>166934</v>
       </c>
       <c r="ED39" t="n">
-        <v>165.906</v>
+        <v>165906</v>
       </c>
       <c r="EE39" t="n">
-        <v>171.106</v>
+        <v>171106</v>
       </c>
       <c r="EF39" t="n">
-        <v>186.792</v>
+        <v>186792</v>
       </c>
       <c r="EG39" t="n">
-        <v>182.543</v>
+        <v>182543</v>
       </c>
       <c r="EH39" t="n">
-        <v>190.07</v>
+        <v>190070</v>
       </c>
       <c r="EI39" t="n">
-        <v>194.963</v>
+        <v>194963</v>
       </c>
       <c r="EJ39" t="n">
-        <v>186.476</v>
+        <v>186476</v>
       </c>
       <c r="EK39" t="n">
-        <v>191.752</v>
+        <v>191752</v>
       </c>
       <c r="EL39" t="n">
-        <v>199.036</v>
+        <v>199036</v>
       </c>
       <c r="EM39" t="n">
-        <v>200.246</v>
+        <v>200246</v>
       </c>
       <c r="EN39" t="n">
-        <v>195.231</v>
+        <v>195231</v>
       </c>
       <c r="EO39" t="n">
-        <v>197.352</v>
+        <v>197352</v>
       </c>
       <c r="EP39" t="n">
-        <v>191.747</v>
+        <v>191747</v>
       </c>
       <c r="EQ39" t="n">
-        <v>189.018</v>
+        <v>189018</v>
       </c>
       <c r="ER39" t="n">
-        <v>197.488</v>
+        <v>197488</v>
       </c>
       <c r="ES39" t="n">
-        <v>189.083</v>
+        <v>189083</v>
       </c>
       <c r="ET39" t="n">
-        <v>209.347</v>
+        <v>209347</v>
       </c>
       <c r="EU39" t="n">
-        <v>201.383</v>
+        <v>201383</v>
       </c>
       <c r="EV39" t="n">
-        <v>204.318</v>
+        <v>204318</v>
       </c>
       <c r="EW39" t="n">
-        <v>206.11</v>
+        <v>206110</v>
       </c>
       <c r="EX39" t="n">
-        <v>209.603</v>
+        <v>209603</v>
       </c>
       <c r="EY39" t="n">
-        <v>216.57</v>
+        <v>216570</v>
       </c>
       <c r="EZ39" t="n">
-        <v>213.016</v>
+        <v>213016</v>
       </c>
       <c r="FA39" t="n">
-        <v>217.491</v>
+        <v>217491</v>
       </c>
       <c r="FB39" t="n">
-        <v>266.407</v>
+        <v>266407</v>
       </c>
       <c r="FC39" t="n">
-        <v>284.526</v>
+        <v>284526</v>
       </c>
       <c r="FD39" t="n">
-        <v>273.903</v>
+        <v>273903</v>
       </c>
       <c r="FE39" t="n">
-        <v>272.345</v>
+        <v>272345</v>
       </c>
       <c r="FF39" t="n">
-        <v>283.268</v>
+        <v>283268</v>
       </c>
       <c r="FG39" t="n">
-        <v>290.808</v>
+        <v>290808</v>
       </c>
       <c r="FH39" t="n">
-        <v>297.13</v>
+        <v>297130</v>
       </c>
       <c r="FI39" t="n">
-        <v>309.668</v>
+        <v>309668</v>
       </c>
       <c r="FJ39" t="n">
-        <v>293.84</v>
+        <v>293840</v>
       </c>
       <c r="FK39" t="n">
-        <v>288.9</v>
+        <v>288900</v>
       </c>
       <c r="FL39" t="n">
-        <v>248.813</v>
+        <v>248813</v>
       </c>
       <c r="FM39" t="n">
-        <v>249.625</v>
+        <v>249625</v>
       </c>
       <c r="FN39" t="n">
-        <v>258.161</v>
+        <v>258161</v>
       </c>
       <c r="FO39" t="n">
-        <v>273.39</v>
+        <v>273390</v>
       </c>
       <c r="FP39" t="n">
-        <v>263.079</v>
+        <v>263079</v>
       </c>
       <c r="FQ39" t="n">
-        <v>269.71</v>
+        <v>269710</v>
       </c>
       <c r="FR39" t="n">
-        <v>272.063</v>
+        <v>272063</v>
       </c>
       <c r="FS39" t="n">
-        <v>283.408</v>
+        <v>283408</v>
       </c>
       <c r="FT39" t="n">
-        <v>281.455</v>
+        <v>281455</v>
       </c>
       <c r="FU39" t="n">
-        <v>282.107</v>
+        <v>282107</v>
       </c>
       <c r="FV39" t="n">
-        <v>303.39</v>
+        <v>303390</v>
       </c>
       <c r="FW39" t="n">
-        <v>320.015</v>
+        <v>320015</v>
       </c>
       <c r="FX39" t="n">
-        <v>343.692</v>
+        <v>343692</v>
       </c>
       <c r="FY39" t="n">
-        <v>345.712</v>
+        <v>345712</v>
       </c>
       <c r="FZ39" t="n">
-        <v>362.792</v>
+        <v>362792</v>
       </c>
       <c r="GA39" t="n">
-        <v>363.41</v>
+        <v>363410</v>
       </c>
       <c r="GB39" t="n">
-        <v>365.384</v>
+        <v>365384</v>
       </c>
       <c r="GC39" t="n">
-        <v>384.032</v>
+        <v>384032</v>
       </c>
       <c r="GD39" t="n">
-        <v>378.246</v>
+        <v>378246</v>
       </c>
       <c r="GE39" t="n">
-        <v>382.367</v>
+        <v>382367</v>
       </c>
       <c r="GF39" t="n">
-        <v>396.216</v>
+        <v>396216</v>
       </c>
       <c r="GG39" t="n">
-        <v>408.323</v>
+        <v>408323</v>
       </c>
       <c r="GH39" t="n">
-        <v>396.838</v>
+        <v>396838</v>
       </c>
       <c r="GI39" t="n">
-        <v>371.196</v>
+        <v>371196</v>
       </c>
       <c r="GJ39" t="n">
-        <v>396.818</v>
+        <v>396818</v>
       </c>
       <c r="GK39" t="n">
-        <v>402.676</v>
+        <v>402676</v>
       </c>
       <c r="GL39" t="n">
-        <v>413.024</v>
+        <v>413024</v>
       </c>
       <c r="GM39" t="n">
-        <v>403.043</v>
+        <v>403043</v>
       </c>
       <c r="GN39" t="n">
-        <v>412.246</v>
+        <v>412246</v>
       </c>
       <c r="GO39" t="n">
-        <v>412.041</v>
+        <v>412041</v>
       </c>
       <c r="GP39" t="n">
-        <v>430.08</v>
+        <v>430080</v>
       </c>
       <c r="GQ39" t="n">
-        <v>435.618</v>
+        <v>435618</v>
       </c>
       <c r="GR39" t="n">
-        <v>436.897</v>
+        <v>436897</v>
       </c>
       <c r="GS39" t="n">
-        <v>438.408</v>
+        <v>438408</v>
       </c>
       <c r="GT39" t="n">
-        <v>451.671</v>
+        <v>451671</v>
       </c>
       <c r="GU39" t="n">
-        <v>589.274</v>
+        <v>589274</v>
       </c>
       <c r="GV39" t="n">
-        <v>532.923</v>
+        <v>532923</v>
       </c>
       <c r="GW39" t="n">
-        <v>545.549</v>
+        <v>545549</v>
       </c>
       <c r="GX39" t="n">
-        <v>552.859</v>
+        <v>552859</v>
       </c>
       <c r="GY39" t="n">
-        <v>553.564</v>
+        <v>553564</v>
       </c>
       <c r="GZ39" t="n">
-        <v>569.606</v>
+        <v>569606</v>
       </c>
       <c r="HA39" t="n">
-        <v>592.498</v>
+        <v>592498</v>
       </c>
     </row>
     <row r="40">
@@ -25675,352 +25675,352 @@
       <c r="CN40"/>
       <c r="CO40"/>
       <c r="CP40" t="n">
-        <v>73.888</v>
+        <v>73888</v>
       </c>
       <c r="CQ40" t="n">
-        <v>76.036</v>
+        <v>76036</v>
       </c>
       <c r="CR40" t="n">
-        <v>80.604</v>
+        <v>80604</v>
       </c>
       <c r="CS40" t="n">
-        <v>84.1</v>
+        <v>84100</v>
       </c>
       <c r="CT40" t="n">
-        <v>78.948</v>
+        <v>78948</v>
       </c>
       <c r="CU40" t="n">
-        <v>81.772</v>
+        <v>81772</v>
       </c>
       <c r="CV40" t="n">
-        <v>82.892</v>
+        <v>82892</v>
       </c>
       <c r="CW40" t="n">
-        <v>85.54</v>
+        <v>85540</v>
       </c>
       <c r="CX40" t="n">
-        <v>90.524</v>
+        <v>90524</v>
       </c>
       <c r="CY40" t="n">
-        <v>90.54</v>
+        <v>90540</v>
       </c>
       <c r="CZ40" t="n">
-        <v>89.28</v>
+        <v>89280</v>
       </c>
       <c r="DA40" t="n">
-        <v>87.568</v>
+        <v>87568</v>
       </c>
       <c r="DB40" t="n">
-        <v>88.772</v>
+        <v>88772</v>
       </c>
       <c r="DC40" t="n">
-        <v>96.376</v>
+        <v>96376</v>
       </c>
       <c r="DD40" t="n">
-        <v>94.872</v>
+        <v>94872</v>
       </c>
       <c r="DE40" t="n">
-        <v>93.892</v>
+        <v>93892</v>
       </c>
       <c r="DF40" t="n">
-        <v>95.98</v>
+        <v>95980</v>
       </c>
       <c r="DG40" t="n">
-        <v>94.924</v>
+        <v>94924</v>
       </c>
       <c r="DH40" t="n">
-        <v>97.108</v>
+        <v>97108</v>
       </c>
       <c r="DI40" t="n">
-        <v>101.384</v>
+        <v>101384</v>
       </c>
       <c r="DJ40" t="n">
-        <v>99.444</v>
+        <v>99444</v>
       </c>
       <c r="DK40" t="n">
-        <v>101.608</v>
+        <v>101608</v>
       </c>
       <c r="DL40" t="n">
-        <v>102.26</v>
+        <v>102260</v>
       </c>
       <c r="DM40" t="n">
-        <v>103.952</v>
+        <v>103952</v>
       </c>
       <c r="DN40" t="n">
-        <v>107.1</v>
+        <v>107100</v>
       </c>
       <c r="DO40" t="n">
-        <v>107.208</v>
+        <v>107208</v>
       </c>
       <c r="DP40" t="n">
-        <v>113.428</v>
+        <v>113428</v>
       </c>
       <c r="DQ40" t="n">
-        <v>114.62</v>
+        <v>114620</v>
       </c>
       <c r="DR40" t="n">
-        <v>114.852</v>
+        <v>114852</v>
       </c>
       <c r="DS40" t="n">
-        <v>116.168</v>
+        <v>116168</v>
       </c>
       <c r="DT40" t="n">
-        <v>125.392</v>
+        <v>125392</v>
       </c>
       <c r="DU40" t="n">
-        <v>121.748</v>
+        <v>121748</v>
       </c>
       <c r="DV40" t="n">
-        <v>129.388</v>
+        <v>129388</v>
       </c>
       <c r="DW40" t="n">
-        <v>132.128</v>
+        <v>132128</v>
       </c>
       <c r="DX40" t="n">
-        <v>133.364</v>
+        <v>133364</v>
       </c>
       <c r="DY40" t="n">
-        <v>143.652</v>
+        <v>143652</v>
       </c>
       <c r="DZ40" t="n">
-        <v>145.547</v>
+        <v>145547</v>
       </c>
       <c r="EA40" t="n">
-        <v>146.352</v>
+        <v>146352</v>
       </c>
       <c r="EB40" t="n">
-        <v>152.896</v>
+        <v>152896</v>
       </c>
       <c r="EC40" t="n">
-        <v>155.307</v>
+        <v>155307</v>
       </c>
       <c r="ED40" t="n">
-        <v>154.378</v>
+        <v>154378</v>
       </c>
       <c r="EE40" t="n">
-        <v>158.02</v>
+        <v>158020</v>
       </c>
       <c r="EF40" t="n">
-        <v>174.229</v>
+        <v>174229</v>
       </c>
       <c r="EG40" t="n">
-        <v>170.506</v>
+        <v>170506</v>
       </c>
       <c r="EH40" t="n">
-        <v>177.772</v>
+        <v>177772</v>
       </c>
       <c r="EI40" t="n">
-        <v>182.692</v>
+        <v>182692</v>
       </c>
       <c r="EJ40" t="n">
-        <v>173.33</v>
+        <v>173330</v>
       </c>
       <c r="EK40" t="n">
-        <v>177.282</v>
+        <v>177282</v>
       </c>
       <c r="EL40" t="n">
-        <v>183.908</v>
+        <v>183908</v>
       </c>
       <c r="EM40" t="n">
-        <v>185.818</v>
+        <v>185818</v>
       </c>
       <c r="EN40" t="n">
-        <v>179.683</v>
+        <v>179683</v>
       </c>
       <c r="EO40" t="n">
-        <v>182.944</v>
+        <v>182944</v>
       </c>
       <c r="EP40" t="n">
-        <v>175.956</v>
+        <v>175956</v>
       </c>
       <c r="EQ40" t="n">
-        <v>176.53</v>
+        <v>176530</v>
       </c>
       <c r="ER40" t="n">
-        <v>186.733</v>
+        <v>186733</v>
       </c>
       <c r="ES40" t="n">
-        <v>177.659</v>
+        <v>177659</v>
       </c>
       <c r="ET40" t="n">
-        <v>200.218</v>
+        <v>200218</v>
       </c>
       <c r="EU40" t="n">
-        <v>190.602</v>
+        <v>190602</v>
       </c>
       <c r="EV40" t="n">
-        <v>194.111</v>
+        <v>194111</v>
       </c>
       <c r="EW40" t="n">
-        <v>196.028</v>
+        <v>196028</v>
       </c>
       <c r="EX40" t="n">
-        <v>200.294</v>
+        <v>200294</v>
       </c>
       <c r="EY40" t="n">
-        <v>203.794</v>
+        <v>203794</v>
       </c>
       <c r="EZ40" t="n">
-        <v>205.059</v>
+        <v>205059</v>
       </c>
       <c r="FA40" t="n">
-        <v>208.505</v>
+        <v>208505</v>
       </c>
       <c r="FB40" t="n">
-        <v>256.944</v>
+        <v>256944</v>
       </c>
       <c r="FC40" t="n">
-        <v>274.664</v>
+        <v>274664</v>
       </c>
       <c r="FD40" t="n">
-        <v>263.924</v>
+        <v>263924</v>
       </c>
       <c r="FE40" t="n">
-        <v>261.944</v>
+        <v>261944</v>
       </c>
       <c r="FF40" t="n">
-        <v>271.844</v>
+        <v>271844</v>
       </c>
       <c r="FG40" t="n">
-        <v>272.456</v>
+        <v>272456</v>
       </c>
       <c r="FH40" t="n">
-        <v>283.691</v>
+        <v>283691</v>
       </c>
       <c r="FI40" t="n">
-        <v>297.609</v>
+        <v>297609</v>
       </c>
       <c r="FJ40" t="n">
-        <v>282.445</v>
+        <v>282445</v>
       </c>
       <c r="FK40" t="n">
-        <v>277.196</v>
+        <v>277196</v>
       </c>
       <c r="FL40" t="n">
-        <v>237.739</v>
+        <v>237739</v>
       </c>
       <c r="FM40" t="n">
-        <v>239.291</v>
+        <v>239291</v>
       </c>
       <c r="FN40" t="n">
-        <v>246.248</v>
+        <v>246248</v>
       </c>
       <c r="FO40" t="n">
-        <v>262.324</v>
+        <v>262324</v>
       </c>
       <c r="FP40" t="n">
-        <v>250.54</v>
+        <v>250540</v>
       </c>
       <c r="FQ40" t="n">
-        <v>259.562</v>
+        <v>259562</v>
       </c>
       <c r="FR40" t="n">
-        <v>258.45</v>
+        <v>258450</v>
       </c>
       <c r="FS40" t="n">
-        <v>270.887</v>
+        <v>270887</v>
       </c>
       <c r="FT40" t="n">
-        <v>269.279</v>
+        <v>269279</v>
       </c>
       <c r="FU40" t="n">
-        <v>269.982</v>
+        <v>269982</v>
       </c>
       <c r="FV40" t="n">
-        <v>291.59</v>
+        <v>291590</v>
       </c>
       <c r="FW40" t="n">
-        <v>307.775</v>
+        <v>307775</v>
       </c>
       <c r="FX40" t="n">
-        <v>332.4</v>
+        <v>332400</v>
       </c>
       <c r="FY40" t="n">
-        <v>335.611</v>
+        <v>335611</v>
       </c>
       <c r="FZ40" t="n">
-        <v>352.188</v>
+        <v>352188</v>
       </c>
       <c r="GA40" t="n">
-        <v>353.442</v>
+        <v>353442</v>
       </c>
       <c r="GB40" t="n">
-        <v>352.909</v>
+        <v>352909</v>
       </c>
       <c r="GC40" t="n">
-        <v>366.274</v>
+        <v>366274</v>
       </c>
       <c r="GD40" t="n">
-        <v>360.221</v>
+        <v>360221</v>
       </c>
       <c r="GE40" t="n">
-        <v>363.844</v>
+        <v>363844</v>
       </c>
       <c r="GF40" t="n">
-        <v>377.967</v>
+        <v>377967</v>
       </c>
       <c r="GG40" t="n">
-        <v>388.176</v>
+        <v>388176</v>
       </c>
       <c r="GH40" t="n">
-        <v>377.158</v>
+        <v>377158</v>
       </c>
       <c r="GI40" t="n">
-        <v>351.783</v>
+        <v>351783</v>
       </c>
       <c r="GJ40" t="n">
-        <v>376.515</v>
+        <v>376515</v>
       </c>
       <c r="GK40" t="n">
-        <v>383.63</v>
+        <v>383630</v>
       </c>
       <c r="GL40" t="n">
-        <v>391.815</v>
+        <v>391815</v>
       </c>
       <c r="GM40" t="n">
-        <v>383.237</v>
+        <v>383237</v>
       </c>
       <c r="GN40" t="n">
-        <v>392.273</v>
+        <v>392273</v>
       </c>
       <c r="GO40" t="n">
-        <v>390.866</v>
+        <v>390866</v>
       </c>
       <c r="GP40" t="n">
-        <v>408.756</v>
+        <v>408756</v>
       </c>
       <c r="GQ40" t="n">
-        <v>413.344</v>
+        <v>413344</v>
       </c>
       <c r="GR40" t="n">
-        <v>418.529</v>
+        <v>418529</v>
       </c>
       <c r="GS40" t="n">
-        <v>413.806</v>
+        <v>413806</v>
       </c>
       <c r="GT40" t="n">
-        <v>428.118</v>
+        <v>428118</v>
       </c>
       <c r="GU40" t="n">
-        <v>502.49</v>
+        <v>502490</v>
       </c>
       <c r="GV40" t="n">
-        <v>481.717</v>
+        <v>481717</v>
       </c>
       <c r="GW40" t="n">
-        <v>507.837</v>
+        <v>507837</v>
       </c>
       <c r="GX40" t="n">
-        <v>511.345</v>
+        <v>511345</v>
       </c>
       <c r="GY40" t="n">
-        <v>520.729</v>
+        <v>520729</v>
       </c>
       <c r="GZ40" t="n">
-        <v>530.821</v>
+        <v>530821</v>
       </c>
       <c r="HA40" t="n">
-        <v>541.892</v>
+        <v>541892</v>
       </c>
     </row>
     <row r="41">
@@ -26028,628 +26028,628 @@
         <v>248</v>
       </c>
       <c r="B41" t="n">
-        <v>5.576</v>
+        <v>5576</v>
       </c>
       <c r="C41" t="n">
-        <v>5.228</v>
+        <v>5228</v>
       </c>
       <c r="D41" t="n">
-        <v>4.816</v>
+        <v>4816</v>
       </c>
       <c r="E41" t="n">
-        <v>4.9</v>
+        <v>4900</v>
       </c>
       <c r="F41" t="n">
-        <v>5.464</v>
+        <v>5464</v>
       </c>
       <c r="G41" t="n">
-        <v>6.312</v>
+        <v>6312</v>
       </c>
       <c r="H41" t="n">
-        <v>5.756</v>
+        <v>5756</v>
       </c>
       <c r="I41" t="n">
-        <v>5.644</v>
+        <v>5644</v>
       </c>
       <c r="J41" t="n">
-        <v>5.668</v>
+        <v>5668</v>
       </c>
       <c r="K41" t="n">
-        <v>5.216</v>
+        <v>5216</v>
       </c>
       <c r="L41" t="n">
-        <v>6.724</v>
+        <v>6724</v>
       </c>
       <c r="M41" t="n">
-        <v>5.7</v>
+        <v>5700</v>
       </c>
       <c r="N41" t="n">
-        <v>5.74</v>
+        <v>5740</v>
       </c>
       <c r="O41" t="n">
-        <v>6.208</v>
+        <v>6208</v>
       </c>
       <c r="P41" t="n">
-        <v>5.344</v>
+        <v>5344</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.92</v>
+        <v>5920</v>
       </c>
       <c r="R41" t="n">
-        <v>7.76</v>
+        <v>7760</v>
       </c>
       <c r="S41" t="n">
-        <v>8.572</v>
+        <v>8572</v>
       </c>
       <c r="T41" t="n">
-        <v>6.496</v>
+        <v>6496</v>
       </c>
       <c r="U41" t="n">
-        <v>7.84</v>
+        <v>7840</v>
       </c>
       <c r="V41" t="n">
-        <v>8.652</v>
+        <v>8652</v>
       </c>
       <c r="W41" t="n">
-        <v>7.804</v>
+        <v>7804</v>
       </c>
       <c r="X41" t="n">
-        <v>10.772</v>
+        <v>10772</v>
       </c>
       <c r="Y41" t="n">
-        <v>10.424</v>
+        <v>10424</v>
       </c>
       <c r="Z41" t="n">
-        <v>10.012</v>
+        <v>10012</v>
       </c>
       <c r="AA41" t="n">
-        <v>9.76</v>
+        <v>9760</v>
       </c>
       <c r="AB41" t="n">
-        <v>10.592</v>
+        <v>10592</v>
       </c>
       <c r="AC41" t="n">
-        <v>11.108</v>
+        <v>11108</v>
       </c>
       <c r="AD41" t="n">
-        <v>10.716</v>
+        <v>10716</v>
       </c>
       <c r="AE41" t="n">
-        <v>10.652</v>
+        <v>10652</v>
       </c>
       <c r="AF41" t="n">
-        <v>11.804</v>
+        <v>11804</v>
       </c>
       <c r="AG41" t="n">
-        <v>10.7</v>
+        <v>10700</v>
       </c>
       <c r="AH41" t="n">
-        <v>10.968</v>
+        <v>10968</v>
       </c>
       <c r="AI41" t="n">
-        <v>11.528</v>
+        <v>11528</v>
       </c>
       <c r="AJ41" t="n">
-        <v>11.908</v>
+        <v>11908</v>
       </c>
       <c r="AK41" t="n">
-        <v>12.528</v>
+        <v>12528</v>
       </c>
       <c r="AL41" t="n">
-        <v>13.592</v>
+        <v>13592</v>
       </c>
       <c r="AM41" t="n">
-        <v>13.048</v>
+        <v>13048</v>
       </c>
       <c r="AN41" t="n">
-        <v>14.292</v>
+        <v>14292</v>
       </c>
       <c r="AO41" t="n">
-        <v>15.752</v>
+        <v>15752</v>
       </c>
       <c r="AP41" t="n">
-        <v>16.26</v>
+        <v>16260</v>
       </c>
       <c r="AQ41" t="n">
-        <v>16.536</v>
+        <v>16536</v>
       </c>
       <c r="AR41" t="n">
-        <v>15.916</v>
+        <v>15916</v>
       </c>
       <c r="AS41" t="n">
-        <v>16.628</v>
+        <v>16628</v>
       </c>
       <c r="AT41" t="n">
-        <v>16.092</v>
+        <v>16092</v>
       </c>
       <c r="AU41" t="n">
-        <v>15.716</v>
+        <v>15716</v>
       </c>
       <c r="AV41" t="n">
-        <v>14.828</v>
+        <v>14828</v>
       </c>
       <c r="AW41" t="n">
-        <v>15.012</v>
+        <v>15012</v>
       </c>
       <c r="AX41" t="n">
-        <v>13.852</v>
+        <v>13852</v>
       </c>
       <c r="AY41" t="n">
-        <v>14.552</v>
+        <v>14552</v>
       </c>
       <c r="AZ41" t="n">
-        <v>14.544</v>
+        <v>14544</v>
       </c>
       <c r="BA41" t="n">
-        <v>14.484</v>
+        <v>14484</v>
       </c>
       <c r="BB41" t="n">
-        <v>15.9</v>
+        <v>15900</v>
       </c>
       <c r="BC41" t="n">
-        <v>14.2</v>
+        <v>14200</v>
       </c>
       <c r="BD41" t="n">
-        <v>15.904</v>
+        <v>15904</v>
       </c>
       <c r="BE41" t="n">
-        <v>15.768</v>
+        <v>15768</v>
       </c>
       <c r="BF41" t="n">
-        <v>16.556</v>
+        <v>16556</v>
       </c>
       <c r="BG41" t="n">
-        <v>17.236</v>
+        <v>17236</v>
       </c>
       <c r="BH41" t="n">
-        <v>18.092</v>
+        <v>18092</v>
       </c>
       <c r="BI41" t="n">
-        <v>18.824</v>
+        <v>18824</v>
       </c>
       <c r="BJ41" t="n">
-        <v>17.044</v>
+        <v>17044</v>
       </c>
       <c r="BK41" t="n">
-        <v>19.408</v>
+        <v>19408</v>
       </c>
       <c r="BL41" t="n">
-        <v>20.036</v>
+        <v>20036</v>
       </c>
       <c r="BM41" t="n">
-        <v>21.184</v>
+        <v>21184</v>
       </c>
       <c r="BN41" t="n">
-        <v>19.72</v>
+        <v>19720</v>
       </c>
       <c r="BO41" t="n">
-        <v>20.556</v>
+        <v>20556</v>
       </c>
       <c r="BP41" t="n">
-        <v>21.284</v>
+        <v>21284</v>
       </c>
       <c r="BQ41" t="n">
-        <v>18.32</v>
+        <v>18320</v>
       </c>
       <c r="BR41" t="n">
-        <v>18.76</v>
+        <v>18760</v>
       </c>
       <c r="BS41" t="n">
-        <v>19.56</v>
+        <v>19560</v>
       </c>
       <c r="BT41" t="n">
-        <v>18.828</v>
+        <v>18828</v>
       </c>
       <c r="BU41" t="n">
-        <v>18.696</v>
+        <v>18696</v>
       </c>
       <c r="BV41" t="n">
-        <v>18.972</v>
+        <v>18972</v>
       </c>
       <c r="BW41" t="n">
-        <v>19.836</v>
+        <v>19836</v>
       </c>
       <c r="BX41" t="n">
-        <v>20.388</v>
+        <v>20388</v>
       </c>
       <c r="BY41" t="n">
-        <v>19.284</v>
+        <v>19284</v>
       </c>
       <c r="BZ41" t="n">
-        <v>20.192</v>
+        <v>20192</v>
       </c>
       <c r="CA41" t="n">
-        <v>19.936</v>
+        <v>19936</v>
       </c>
       <c r="CB41" t="n">
-        <v>18.832</v>
+        <v>18832</v>
       </c>
       <c r="CC41" t="n">
-        <v>20.492</v>
+        <v>20492</v>
       </c>
       <c r="CD41" t="n">
-        <v>21.448</v>
+        <v>21448</v>
       </c>
       <c r="CE41" t="n">
-        <v>20.184</v>
+        <v>20184</v>
       </c>
       <c r="CF41" t="n">
-        <v>20.508</v>
+        <v>20508</v>
       </c>
       <c r="CG41" t="n">
-        <v>21.188</v>
+        <v>21188</v>
       </c>
       <c r="CH41" t="n">
-        <v>21.552</v>
+        <v>21552</v>
       </c>
       <c r="CI41" t="n">
-        <v>21.612</v>
+        <v>21612</v>
       </c>
       <c r="CJ41" t="n">
-        <v>21.056</v>
+        <v>21056</v>
       </c>
       <c r="CK41" t="n">
-        <v>20.612</v>
+        <v>20612</v>
       </c>
       <c r="CL41" t="n">
-        <v>21.388</v>
+        <v>21388</v>
       </c>
       <c r="CM41" t="n">
-        <v>22.8</v>
+        <v>22800</v>
       </c>
       <c r="CN41" t="n">
-        <v>22.288</v>
+        <v>22288</v>
       </c>
       <c r="CO41" t="n">
-        <v>23.064</v>
+        <v>23064</v>
       </c>
       <c r="CP41" t="n">
-        <v>21.784</v>
+        <v>21784</v>
       </c>
       <c r="CQ41" t="n">
-        <v>22.472</v>
+        <v>22472</v>
       </c>
       <c r="CR41" t="n">
-        <v>24.884</v>
+        <v>24884</v>
       </c>
       <c r="CS41" t="n">
-        <v>24.764</v>
+        <v>24764</v>
       </c>
       <c r="CT41" t="n">
-        <v>23.632</v>
+        <v>23632</v>
       </c>
       <c r="CU41" t="n">
-        <v>23.952</v>
+        <v>23952</v>
       </c>
       <c r="CV41" t="n">
-        <v>25.152</v>
+        <v>25152</v>
       </c>
       <c r="CW41" t="n">
-        <v>26.476</v>
+        <v>26476</v>
       </c>
       <c r="CX41" t="n">
-        <v>27.744</v>
+        <v>27744</v>
       </c>
       <c r="CY41" t="n">
-        <v>28.028</v>
+        <v>28028</v>
       </c>
       <c r="CZ41" t="n">
-        <v>26.448</v>
+        <v>26448</v>
       </c>
       <c r="DA41" t="n">
-        <v>26.816</v>
+        <v>26816</v>
       </c>
       <c r="DB41" t="n">
-        <v>29.136</v>
+        <v>29136</v>
       </c>
       <c r="DC41" t="n">
-        <v>27.904</v>
+        <v>27904</v>
       </c>
       <c r="DD41" t="n">
-        <v>27.116</v>
+        <v>27116</v>
       </c>
       <c r="DE41" t="n">
-        <v>28.72</v>
+        <v>28720</v>
       </c>
       <c r="DF41" t="n">
-        <v>28.4</v>
+        <v>28400</v>
       </c>
       <c r="DG41" t="n">
-        <v>29.016</v>
+        <v>29016</v>
       </c>
       <c r="DH41" t="n">
-        <v>29.084</v>
+        <v>29084</v>
       </c>
       <c r="DI41" t="n">
-        <v>28.744</v>
+        <v>28744</v>
       </c>
       <c r="DJ41" t="n">
-        <v>27.052</v>
+        <v>27052</v>
       </c>
       <c r="DK41" t="n">
-        <v>27.336</v>
+        <v>27336</v>
       </c>
       <c r="DL41" t="n">
-        <v>29.104</v>
+        <v>29104</v>
       </c>
       <c r="DM41" t="n">
-        <v>31.232</v>
+        <v>31232</v>
       </c>
       <c r="DN41" t="n">
-        <v>27.78</v>
+        <v>27780</v>
       </c>
       <c r="DO41" t="n">
-        <v>32.192</v>
+        <v>32192</v>
       </c>
       <c r="DP41" t="n">
-        <v>34.264</v>
+        <v>34264</v>
       </c>
       <c r="DQ41" t="n">
-        <v>34.124</v>
+        <v>34124</v>
       </c>
       <c r="DR41" t="n">
-        <v>35.572</v>
+        <v>35572</v>
       </c>
       <c r="DS41" t="n">
-        <v>36.04</v>
+        <v>36040</v>
       </c>
       <c r="DT41" t="n">
-        <v>35.728</v>
+        <v>35728</v>
       </c>
       <c r="DU41" t="n">
-        <v>39.26</v>
+        <v>39260</v>
       </c>
       <c r="DV41" t="n">
-        <v>40.316</v>
+        <v>40316</v>
       </c>
       <c r="DW41" t="n">
-        <v>43.008</v>
+        <v>43008</v>
       </c>
       <c r="DX41" t="n">
-        <v>42.668</v>
+        <v>42668</v>
       </c>
       <c r="DY41" t="n">
-        <v>43.008</v>
+        <v>43008</v>
       </c>
       <c r="DZ41" t="n">
-        <v>50.609</v>
+        <v>50609</v>
       </c>
       <c r="EA41" t="n">
-        <v>45.405</v>
+        <v>45405</v>
       </c>
       <c r="EB41" t="n">
-        <v>41.342</v>
+        <v>41342</v>
       </c>
       <c r="EC41" t="n">
-        <v>44.814</v>
+        <v>44814</v>
       </c>
       <c r="ED41" t="n">
-        <v>43.171</v>
+        <v>43171</v>
       </c>
       <c r="EE41" t="n">
-        <v>48.719</v>
+        <v>48719</v>
       </c>
       <c r="EF41" t="n">
-        <v>46.443</v>
+        <v>46443</v>
       </c>
       <c r="EG41" t="n">
-        <v>45.507</v>
+        <v>45507</v>
       </c>
       <c r="EH41" t="n">
-        <v>47.601</v>
+        <v>47601</v>
       </c>
       <c r="EI41" t="n">
-        <v>44.213</v>
+        <v>44213</v>
       </c>
       <c r="EJ41" t="n">
-        <v>50.413</v>
+        <v>50413</v>
       </c>
       <c r="EK41" t="n">
-        <v>44.947</v>
+        <v>44947</v>
       </c>
       <c r="EL41" t="n">
-        <v>49.943</v>
+        <v>49943</v>
       </c>
       <c r="EM41" t="n">
-        <v>51.172</v>
+        <v>51172</v>
       </c>
       <c r="EN41" t="n">
-        <v>47.383</v>
+        <v>47383</v>
       </c>
       <c r="EO41" t="n">
-        <v>49.225</v>
+        <v>49225</v>
       </c>
       <c r="EP41" t="n">
-        <v>53.557</v>
+        <v>53557</v>
       </c>
       <c r="EQ41" t="n">
-        <v>53.237</v>
+        <v>53237</v>
       </c>
       <c r="ER41" t="n">
-        <v>52.165</v>
+        <v>52165</v>
       </c>
       <c r="ES41" t="n">
-        <v>51.704</v>
+        <v>51704</v>
       </c>
       <c r="ET41" t="n">
-        <v>50.937</v>
+        <v>50937</v>
       </c>
       <c r="EU41" t="n">
-        <v>56.121</v>
+        <v>56121</v>
       </c>
       <c r="EV41" t="n">
-        <v>55.528</v>
+        <v>55528</v>
       </c>
       <c r="EW41" t="n">
-        <v>54.619</v>
+        <v>54619</v>
       </c>
       <c r="EX41" t="n">
-        <v>56.613</v>
+        <v>56613</v>
       </c>
       <c r="EY41" t="n">
-        <v>58.842</v>
+        <v>58842</v>
       </c>
       <c r="EZ41" t="n">
-        <v>56.868</v>
+        <v>56868</v>
       </c>
       <c r="FA41" t="n">
-        <v>58.177</v>
+        <v>58177</v>
       </c>
       <c r="FB41" t="n">
-        <v>58.334</v>
+        <v>58334</v>
       </c>
       <c r="FC41" t="n">
-        <v>59.643</v>
+        <v>59643</v>
       </c>
       <c r="FD41" t="n">
-        <v>67.126</v>
+        <v>67126</v>
       </c>
       <c r="FE41" t="n">
-        <v>68.543</v>
+        <v>68543</v>
       </c>
       <c r="FF41" t="n">
-        <v>64.721</v>
+        <v>64721</v>
       </c>
       <c r="FG41" t="n">
-        <v>73.737</v>
+        <v>73737</v>
       </c>
       <c r="FH41" t="n">
-        <v>74.821</v>
+        <v>74821</v>
       </c>
       <c r="FI41" t="n">
-        <v>75.022</v>
+        <v>75022</v>
       </c>
       <c r="FJ41" t="n">
-        <v>70.503</v>
+        <v>70503</v>
       </c>
       <c r="FK41" t="n">
-        <v>69.145</v>
+        <v>69145</v>
       </c>
       <c r="FL41" t="n">
-        <v>65.916</v>
+        <v>65916</v>
       </c>
       <c r="FM41" t="n">
-        <v>70.531</v>
+        <v>70531</v>
       </c>
       <c r="FN41" t="n">
-        <v>67.107</v>
+        <v>67107</v>
       </c>
       <c r="FO41" t="n">
-        <v>67.67</v>
+        <v>67670</v>
       </c>
       <c r="FP41" t="n">
-        <v>65.88</v>
+        <v>65880</v>
       </c>
       <c r="FQ41" t="n">
-        <v>65.507</v>
+        <v>65507</v>
       </c>
       <c r="FR41" t="n">
-        <v>67.564</v>
+        <v>67564</v>
       </c>
       <c r="FS41" t="n">
-        <v>63.979</v>
+        <v>63979</v>
       </c>
       <c r="FT41" t="n">
-        <v>68.014</v>
+        <v>68014</v>
       </c>
       <c r="FU41" t="n">
-        <v>65.742</v>
+        <v>65742</v>
       </c>
       <c r="FV41" t="n">
-        <v>65.276</v>
+        <v>65276</v>
       </c>
       <c r="FW41" t="n">
-        <v>67.164</v>
+        <v>67164</v>
       </c>
       <c r="FX41" t="n">
-        <v>68.84</v>
+        <v>68840</v>
       </c>
       <c r="FY41" t="n">
-        <v>61.403</v>
+        <v>61403</v>
       </c>
       <c r="FZ41" t="n">
-        <v>63.534</v>
+        <v>63534</v>
       </c>
       <c r="GA41" t="n">
-        <v>62.907</v>
+        <v>62907</v>
       </c>
       <c r="GB41" t="n">
-        <v>66.76</v>
+        <v>66760</v>
       </c>
       <c r="GC41" t="n">
-        <v>64.462</v>
+        <v>64462</v>
       </c>
       <c r="GD41" t="n">
-        <v>66.301</v>
+        <v>66301</v>
       </c>
       <c r="GE41" t="n">
-        <v>67.191</v>
+        <v>67191</v>
       </c>
       <c r="GF41" t="n">
-        <v>68.578</v>
+        <v>68578</v>
       </c>
       <c r="GG41" t="n">
-        <v>66.981</v>
+        <v>66981</v>
       </c>
       <c r="GH41" t="n">
-        <v>66.664</v>
+        <v>66664</v>
       </c>
       <c r="GI41" t="n">
-        <v>68.964</v>
+        <v>68964</v>
       </c>
       <c r="GJ41" t="n">
-        <v>64.058</v>
+        <v>64058</v>
       </c>
       <c r="GK41" t="n">
-        <v>64.983</v>
+        <v>64983</v>
       </c>
       <c r="GL41" t="n">
-        <v>64.022</v>
+        <v>64022</v>
       </c>
       <c r="GM41" t="n">
-        <v>65.008</v>
+        <v>65008</v>
       </c>
       <c r="GN41" t="n">
-        <v>69.409</v>
+        <v>69409</v>
       </c>
       <c r="GO41" t="n">
-        <v>64.797</v>
+        <v>64797</v>
       </c>
       <c r="GP41" t="n">
-        <v>66.022</v>
+        <v>66022</v>
       </c>
       <c r="GQ41" t="n">
-        <v>66.851</v>
+        <v>66851</v>
       </c>
       <c r="GR41" t="n">
-        <v>69.611</v>
+        <v>69611</v>
       </c>
       <c r="GS41" t="n">
-        <v>70.894</v>
+        <v>70894</v>
       </c>
       <c r="GT41" t="n">
-        <v>72.774</v>
+        <v>72774</v>
       </c>
       <c r="GU41" t="n">
-        <v>75.275</v>
+        <v>75275</v>
       </c>
       <c r="GV41" t="n">
-        <v>78.767</v>
+        <v>78767</v>
       </c>
       <c r="GW41" t="n">
-        <v>76.995</v>
+        <v>76995</v>
       </c>
       <c r="GX41" t="n">
-        <v>75.03</v>
+        <v>75030</v>
       </c>
       <c r="GY41" t="n">
-        <v>77.704</v>
+        <v>77704</v>
       </c>
       <c r="GZ41" t="n">
-        <v>72.767</v>
+        <v>72767</v>
       </c>
       <c r="HA41" t="n">
-        <v>73.727</v>
+        <v>73727</v>
       </c>
     </row>
     <row r="42">
